--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_18-07-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -780,12 +780,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1143,17 +1143,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1869,29 +1869,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£34.99</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£34.99</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£34.99</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£44.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>£35.85</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£44.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£35.85</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>£34.99</t>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>£43.99 presale price: £72.38</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff7df41e925+77845]
+	GetHandleVerifier [0x0x7ff7df41e980+77936]
+	(No symbol) [0x0x7ff7df1d9cda]
+	(No symbol) [0x0x7ff7df2306aa]
+	(No symbol) [0x0x7ff7df23095c]
+	(No symbol) [0x0x7ff7df283d07]
+	(No symbol) [0x0x7ff7df25890f]
+	(No symbol) [0x0x7ff7df280b07]
+	(No symbol) [0x0x7ff7df2586a3]
+	(No symbol) [0x0x7ff7df221791]
+	(No symbol) [0x0x7ff7df222523]
+	GetHandleVerifier [0x0x7ff7df6f683d+3059501]
+	GetHandleVerifier [0x0x7ff7df6f0bfd+3035885]
+	GetHandleVerifier [0x0x7ff7df7103f0+3164896]
+	GetHandleVerifier [0x0x7ff7df438c2e+185118]
+	GetHandleVerifier [0x0x7ff7df44053f+216111]
+	GetHandleVerifier [0x0x7ff7df4272d4+113092]
+	GetHandleVerifier [0x0x7ff7df427489+113529]
+	GetHandleVerifier [0x0x7ff7df40e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
